--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105965641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105965638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105965640</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,48 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105965638</v>
+        <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Orsa, Ackamäck, Dlr</t>
+          <t>Ackomäck, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478247</v>
+        <v>478264</v>
       </c>
       <c r="R3" t="n">
-        <v>6819246</v>
+        <v>6819280</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-27</t>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +877,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/105965638</t>
+          <t>https://artportalen.se/Sighting/135864528</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105965640</v>
+        <v>105965638</v>
       </c>
       <c r="B4" t="n">
-        <v>80461</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478252</v>
+        <v>478247</v>
       </c>
       <c r="R4" t="n">
-        <v>6819240</v>
+        <v>6819246</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,7 +990,1239 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/105965638</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135864525</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>478261</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6819249</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864525</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135864526</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>478261</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6819251</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864526</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135864529</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>478264</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6819278</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864529</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135864531</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>478235</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6819280</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864531</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135864534</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>478203</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6819243</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864534</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135864535</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>478183</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6819224</v>
+      </c>
+      <c r="S10" t="n">
+        <v>19</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864535</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135864527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>478274</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6819289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864527</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105965640</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Orsa, Ackamäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>478252</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6819240</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-07-27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/105965640</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135864524</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478248</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6819230</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864524</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135864536</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478177</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6819125</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864536</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135864533</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ackomäck, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478226</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6819253</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135864533</t>
         </is>
       </c>
     </row>
@@ -989,6 +2231,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98165</v>
+        <v>98176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79486</v>
+        <v>79492</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98176</v>
+        <v>98189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>135864524</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>135864536</v>
       </c>
       <c r="B14" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 30158-2026 artfynd.xlsx
+++ b/artfynd/A 30158-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135864528</v>
       </c>
       <c r="B3" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135864525</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>135864526</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135864529</v>
       </c>
       <c r="B7" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>135864531</v>
       </c>
       <c r="B8" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135864534</v>
       </c>
       <c r="B9" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135864535</v>
       </c>
       <c r="B10" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135864527</v>
       </c>
       <c r="B11" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135864533</v>
       </c>
       <c r="B15" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
